--- a/doc/Микросхемы/ЮТ-88/ЮТ-88.xlsx
+++ b/doc/Микросхемы/ЮТ-88/ЮТ-88.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\Микросхемы\ЮТ-88\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My\Spectrum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8F951F-D322-4255-ADAD-F54BEF94A9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11175" yWindow="2955" windowWidth="19170" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,11 +24,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">К176ИЕ5    </t>
+  </si>
+  <si>
+    <t>К155ТМ2</t>
+  </si>
+  <si>
+    <t>К155ИД3</t>
+  </si>
   <si>
     <t>Кол-во</t>
   </si>
   <si>
+    <t>КР556РТ5</t>
+  </si>
+  <si>
+    <t>К155ЛА8</t>
+  </si>
+  <si>
+    <t>КР541РУ2</t>
+  </si>
+  <si>
+    <t>К155РП1</t>
+  </si>
+  <si>
+    <t>К155ИД4</t>
+  </si>
+  <si>
+    <t>К155ЛЕ4</t>
+  </si>
+  <si>
+    <t>К155ИЕ5</t>
+  </si>
+  <si>
+    <t>К155ЛА3</t>
+  </si>
+  <si>
+    <t>К155ЛА2</t>
+  </si>
+  <si>
+    <t>КР565РУ6Д</t>
+  </si>
+  <si>
+    <t>К155ЛП5</t>
+  </si>
+  <si>
+    <t>К155ИР13</t>
+  </si>
+  <si>
+    <t>К155ИМ3</t>
+  </si>
+  <si>
+    <t>К155ЛА1</t>
+  </si>
+  <si>
+    <t>КР580ВВ55</t>
+  </si>
+  <si>
+    <t>К589АП16</t>
+  </si>
+  <si>
     <t>ru-chipdip</t>
   </si>
   <si>
@@ -39,6 +95,18 @@
     <t>ay.by</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>74LS170 aliexpress</t>
+  </si>
+  <si>
+    <t>74LS27 aliexpress</t>
+  </si>
+  <si>
+    <t>74LS83 aliexpress</t>
+  </si>
+  <si>
     <t>КТ315А</t>
   </si>
   <si>
@@ -109,12 +177,18 @@
   </si>
   <si>
     <t>6-25 пФ</t>
+  </si>
+  <si>
+    <t>14-30</t>
+  </si>
+  <si>
+    <t>16-22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -148,10 +222,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -431,8 +507,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -442,201 +518,569 @@
     <col min="8" max="8" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="E3">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.0013888888888889</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="E5">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.83472222222222225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.66805555555555562</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1.007638888888889</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="E7">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1.1673611111111111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="K8" s="4">
+        <v>1.6680555555555554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="E9">
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.58680555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="E10">
+        <v>0.15</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.58819444444444446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>0.21</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.58402777777777781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="E12">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.58402777777777781</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="E13">
+        <v>0.21</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1.0006944444444443</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.66805555555555562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="E15">
+        <v>0.21</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.5854166666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="E17">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.58402777777777781</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B11">
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.75555555555555554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1.0020833333333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="E23">
+        <v>0.3</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.67222222222222217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1.6673611111111111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.63</v>
+      </c>
+      <c r="E27">
+        <v>0.16</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0.66805555555555562</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36">
         <v>42</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C36" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20">
+      <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>26</v>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
